--- a/data/05_modelado/results/results_mlp_ebm.xlsx
+++ b/data/05_modelado/results/results_mlp_ebm.xlsx
@@ -568,7 +568,7 @@
         <v>0.8980889055676384</v>
       </c>
       <c r="K2" t="n">
-        <v>6.195</v>
+        <v>5.683</v>
       </c>
       <c r="L2" t="n">
         <v>6.91</v>
@@ -636,10 +636,10 @@
         <v>0.8980889055676384</v>
       </c>
       <c r="K3" t="n">
-        <v>6.972</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="M3" t="n">
         <v>0.8310999999999999</v>
@@ -704,7 +704,7 @@
         <v>0.8920655709833989</v>
       </c>
       <c r="K4" t="n">
-        <v>1777.304</v>
+        <v>512.799</v>
       </c>
       <c r="L4" t="n">
         <v>6.65</v>
@@ -772,10 +772,10 @@
         <v>0.885819623470318</v>
       </c>
       <c r="K5" t="n">
-        <v>19.323</v>
+        <v>23.548</v>
       </c>
       <c r="L5" t="n">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="M5" t="n">
         <v>0.8193</v>
@@ -840,7 +840,7 @@
         <v>0.8899463146989774</v>
       </c>
       <c r="K6" t="n">
-        <v>280.69</v>
+        <v>205.061</v>
       </c>
       <c r="L6" t="n">
         <v>6.79</v>
@@ -908,7 +908,7 @@
         <v>0.8899463146989774</v>
       </c>
       <c r="K7" t="n">
-        <v>428.258</v>
+        <v>231.967</v>
       </c>
       <c r="L7" t="n">
         <v>6.65</v>
